--- a/src/test/resources/test-data/cargoRunner/DataCreation.xlsx
+++ b/src/test/resources/test-data/cargoRunner/DataCreation.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91902\IdeaProjects\Selenium_E2E_Automation_framework\src\test\resources\test-data\cargoRunner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B8C5AF-F83E-4C11-8931-0C290108BF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B31D15D-EE12-44B4-857E-2B750F2EB8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="57">
   <si>
     <t>TestName</t>
   </si>
@@ -106,25 +107,97 @@
     <t>New msg</t>
   </si>
   <si>
-    <t>milestone</t>
-  </si>
-  <si>
     <t>Hello milestone</t>
   </si>
   <si>
-    <t>wow milestone</t>
-  </si>
-  <si>
     <t>rock milestone</t>
   </si>
   <si>
     <t>create mielstone</t>
   </si>
   <si>
-    <t>fine with</t>
-  </si>
-  <si>
     <t>ok done</t>
+  </si>
+  <si>
+    <t>Task Name</t>
+  </si>
+  <si>
+    <t>Task Code</t>
+  </si>
+  <si>
+    <t>Task Description</t>
+  </si>
+  <si>
+    <t>Workflow type</t>
+  </si>
+  <si>
+    <t>Performed By</t>
+  </si>
+  <si>
+    <t>Container Level</t>
+  </si>
+  <si>
+    <t>Email task</t>
+  </si>
+  <si>
+    <t>Ravi</t>
+  </si>
+  <si>
+    <t>new Discription</t>
+  </si>
+  <si>
+    <t>GSC</t>
+  </si>
+  <si>
+    <t>CSO</t>
+  </si>
+  <si>
+    <t>GSC &amp; CSO</t>
+  </si>
+  <si>
+    <t>SAM</t>
+  </si>
+  <si>
+    <t>csz</t>
+  </si>
+  <si>
+    <t>abo</t>
+  </si>
+  <si>
+    <t>csg</t>
+  </si>
+  <si>
+    <t>lel</t>
+  </si>
+  <si>
+    <t>lol</t>
+  </si>
+  <si>
+    <t>bunti</t>
+  </si>
+  <si>
+    <t>nik</t>
+  </si>
+  <si>
+    <t>hok</t>
+  </si>
+  <si>
+    <t>kif</t>
+  </si>
+  <si>
+    <t>bne</t>
+  </si>
+  <si>
+    <t>teas</t>
+  </si>
+  <si>
+    <t>fre</t>
+  </si>
+  <si>
+    <t>odea</t>
+  </si>
+  <si>
+    <t>try new things</t>
   </si>
 </sst>
 </file>
@@ -564,9 +637,6 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
       <c r="E3" s="1" t="b">
         <v>0</v>
       </c>
@@ -585,7 +655,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -604,9 +674,6 @@
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
       <c r="E5" s="1" t="b">
         <v>0</v>
       </c>
@@ -625,7 +692,7 @@
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -645,7 +712,7 @@
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="b">
         <v>0</v>
@@ -664,9 +731,6 @@
       <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
@@ -685,12 +749,330 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE38786F-3FA4-43DB-B7F0-2AC131FE21B5}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="1" t="b">
-        <v>0</v>
+      <c r="D1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2">
+        <v>3013</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3">
+        <v>3021</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4">
+        <v>3025</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5">
+        <v>3028</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6">
+        <v>2103</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7">
+        <v>9341</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8">
+        <v>1102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9">
+        <v>3409</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
       </c>
       <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10">
+        <v>2391</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="b">
         <v>0</v>
       </c>
     </row>
